--- a/Config/Excel/GameConfig/ResourceConfig.xlsx
+++ b/Config/Excel/GameConfig/ResourceConfig.xlsx
@@ -1,130 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\DX01DemoProj\Unity\LubanExcel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24D9F1C-5BC9-4A1B-86AD-E67F4561115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>##var</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>##type</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试说明</t>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Url</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 资源路径</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Bundles/Scenes/Map1.unity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,43 +100,102 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="差" xfId="1" builtinId="27"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -479,73 +485,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="17.125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="28.625" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="7.875" customWidth="1" style="2" min="5" max="5"/>
+    <col width="6.5" customWidth="1" style="2" min="6" max="6"/>
+    <col width="6.625" customWidth="1" style="2" min="7" max="7"/>
+    <col width="9" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1">
+    <row r="1" ht="16.5" customFormat="1" customHeight="1" s="3">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 资源路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>测试说明</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Scenes/Map1.unity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>掉落表_1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>掉落表_1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>掉落表_1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>掉落表_1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>掉落表_1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>关卡奖励_5001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>关卡奖励_5002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>5003</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>关卡奖励_5003</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>